--- a/data/trans_camb/KIDM_C_3_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 16,56</t>
+          <t>-1,12; 16,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 7,99</t>
+          <t>-6,83; 7,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 1,91</t>
+          <t>-10,64; 2,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 7,39</t>
+          <t>-6,11; 7,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 13,18</t>
+          <t>-2,52; 13,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 7,13</t>
+          <t>-7,91; 6,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 9,35</t>
+          <t>-1,4; 9,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 8,36</t>
+          <t>-2,71; 7,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,42</t>
+          <t>-7,28; 3,33</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 636,49</t>
+          <t>-31,13; 521,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 289,35</t>
+          <t>-74,79; 243,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-64,12; 260,0</t>
+          <t>-67,04; 267,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 408,75</t>
+          <t>-35,49; 353,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 259,51</t>
+          <t>-100,0; 215,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,08; 224,08</t>
+          <t>-21,01; 220,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 208,16</t>
+          <t>-36,39; 190,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-88,09; 72,01</t>
+          <t>-86,65; 99,79</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 13,27</t>
+          <t>-0,04; 12,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,76</t>
+          <t>-3,99; 6,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 8,15</t>
+          <t>-6,26; 8,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,17; 22,29</t>
+          <t>8,43; 22,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 14,25</t>
+          <t>2,4; 14,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,35; -0,69</t>
+          <t>-7,39; -0,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,78; 15,59</t>
+          <t>5,86; 15,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 8,59</t>
+          <t>-0,01; 8,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,78</t>
+          <t>-5,71; 0,89</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 364,35</t>
+          <t>-7,16; 328,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,06; 184,96</t>
+          <t>-47,06; 183,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,52; 211,22</t>
+          <t>-75,78; 230,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112,42; 1411,41</t>
+          <t>109,03; 1510,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 840,93</t>
+          <t>27,02; 1089,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,4; 451,15</t>
+          <t>73,34; 463,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 250,18</t>
+          <t>-3,41; 249,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-82,12; 49,02</t>
+          <t>-83,19; 33,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,71; 24,01</t>
+          <t>6,13; 24,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 13,1</t>
+          <t>-1,99; 12,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 2,59</t>
+          <t>-9,43; 2,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 14,59</t>
+          <t>1,43; 15,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 14,71</t>
+          <t>0,77; 14,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 0,41</t>
+          <t>-7,23; 0,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68; 17,2</t>
+          <t>5,45; 17,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,12</t>
+          <t>1,2; 11,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,62</t>
+          <t>-5,86; 0,59</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,0; 1584,75</t>
+          <t>39,07; 1507,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,47; 861,06</t>
+          <t>-38,62; 672,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 1468,74</t>
+          <t>-4,93; 1632,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 1561,87</t>
+          <t>-25,43; 1366,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,11; 867,48</t>
+          <t>77,05; 1015,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,73; 554,58</t>
+          <t>5,92; 683,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,38</t>
+          <t>-100,0; 98,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 20,53</t>
+          <t>5,22; 20,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 14,24</t>
+          <t>1,14; 14,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 7,04</t>
+          <t>-4,54; 7,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 10,71</t>
+          <t>-0,94; 11,12</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 9,64</t>
+          <t>-1,86; 9,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,72</t>
+          <t>-5,03; 6,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,49</t>
+          <t>4,19; 14,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,37</t>
+          <t>0,96; 9,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,69</t>
+          <t>-3,71; 4,92</t>
         </is>
       </c>
     </row>
@@ -1431,27 +1431,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>53,63; 1478,73</t>
+          <t>51,14; 1630,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1111,35</t>
+          <t>2,23; 1056,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 557,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 653,75</t>
+          <t>-36,16; 718,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,16; 620,28</t>
+          <t>-41,63; 606,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,78; 605,73</t>
+          <t>63,35; 648,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,01; 487,4</t>
+          <t>12,72; 449,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,61; 212,49</t>
+          <t>-72,99; 259,18</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,84</t>
+          <t>5,73; 14,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,06</t>
+          <t>0,07; 6,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,59</t>
+          <t>-4,67; 1,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,44; 11,2</t>
+          <t>4,41; 10,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,44</t>
+          <t>2,93; 9,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,24</t>
+          <t>-4,45; 0,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,18</t>
+          <t>6,32; 11,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,24</t>
+          <t>2,67; 7,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,14</t>
+          <t>-3,81; -0,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>74,14; 337,35</t>
+          <t>76,44; 371,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,81; 178,07</t>
+          <t>0,07; 172,09</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 42,34</t>
+          <t>-69,66; 54,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77,78; 391,32</t>
+          <t>76,31; 381,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>47,93; 331,01</t>
+          <t>51,34; 318,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-82,65; 15,25</t>
+          <t>-83,69; 18,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>102,56; 295,18</t>
+          <t>107,26; 303,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>42,07; 190,47</t>
+          <t>49,16; 186,77</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-69,57; -2,86</t>
+          <t>-68,43; 0,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_C_3_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Habitat-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 16,54</t>
+          <t>-0,39; 16,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 7,25</t>
+          <t>-6,52; 8,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 2,01</t>
+          <t>-10,74; 2,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 7,61</t>
+          <t>-5,88; 7,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 13,24</t>
+          <t>-2,98; 12,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 6,84</t>
+          <t>-8,19; 5,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 9,54</t>
+          <t>-1,35; 9,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 7,72</t>
+          <t>-2,83; 7,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 3,33</t>
+          <t>-7,27; 3,14</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,13; 521,46</t>
+          <t>-13,9; 625,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 243,31</t>
+          <t>-73,58; 283,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,04; 267,81</t>
+          <t>-61,78; 248,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 353,76</t>
+          <t>-43,2; 364,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 215,31</t>
+          <t>-100,0; 218,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 220,05</t>
+          <t>-23,18; 213,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,39; 190,95</t>
+          <t>-39,25; 181,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 99,79</t>
+          <t>-86,23; 93,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 12,57</t>
+          <t>-0,7; 12,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 6,6</t>
+          <t>-4,19; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 8,01</t>
+          <t>-5,48; 8,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,43; 22,68</t>
+          <t>8,68; 23,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,76</t>
+          <t>2,22; 14,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -0,27</t>
+          <t>-7,39; -0,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,86; 15,5</t>
+          <t>6,28; 15,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 8,46</t>
+          <t>0,57; 9,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 0,89</t>
+          <t>-5,64; 0,78</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 328,73</t>
+          <t>-15,56; 312,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-47,06; 183,29</t>
+          <t>-51,1; 171,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,78; 230,82</t>
+          <t>-68,15; 302,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109,03; 1510,3</t>
+          <t>115,45; 1403,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,02; 1089,88</t>
+          <t>19,51; 988,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,34; 463,88</t>
+          <t>77,84; 475,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 249,4</t>
+          <t>2,3; 261,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 33,25</t>
+          <t>-82,66; 38,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,13; 24,27</t>
+          <t>6,78; 24,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 12,91</t>
+          <t>-1,39; 12,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 2,07</t>
+          <t>-9,31; 2,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 15,02</t>
+          <t>1,57; 15,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 14,85</t>
+          <t>0,54; 14,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 0,01</t>
+          <t>-7,26; 0,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 17,18</t>
+          <t>5,2; 16,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,49</t>
+          <t>1,03; 11,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 0,59</t>
+          <t>-5,93; 0,79</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,07; 1507,44</t>
+          <t>48,41; 1433,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,62; 672,52</t>
+          <t>-33,85; 720,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,12 +1230,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 1632,71</t>
+          <t>-3,17; 1526,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 1366,3</t>
+          <t>-11,02; 1457,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>77,05; 1015,25</t>
+          <t>85,01; 915,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,92; 683,34</t>
+          <t>8,66; 649,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,22</t>
+          <t>-100,0; 102,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 20,49</t>
+          <t>3,94; 20,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 14,59</t>
+          <t>1,25; 14,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 7,44</t>
+          <t>-4,88; 6,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 11,12</t>
+          <t>-0,44; 11,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 9,24</t>
+          <t>-1,32; 9,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 6,4</t>
+          <t>-4,56; 6,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,19; 14,09</t>
+          <t>4,03; 14,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,99</t>
+          <t>1,83; 10,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 4,92</t>
+          <t>-3,45; 4,65</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>51,14; 1630,31</t>
+          <t>34,77; 1514,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 1056,37</t>
+          <t>4,23; 1248,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 718,56</t>
+          <t>-24,2; 678,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 606,19</t>
+          <t>-26,84; 692,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 572,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,35; 648,88</t>
+          <t>64,01; 651,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>12,72; 449,41</t>
+          <t>27,36; 481,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-72,99; 259,18</t>
+          <t>-74,1; 220,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,1</t>
+          <t>6,09; 13,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,93</t>
+          <t>0,29; 7,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,92</t>
+          <t>-4,77; 1,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,81</t>
+          <t>4,04; 11,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,14</t>
+          <t>2,88; 9,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,2</t>
+          <t>-4,44; 0,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,51</t>
+          <t>6,02; 11,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,25</t>
+          <t>2,42; 7,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,08</t>
+          <t>-3,98; 0,02</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>76,44; 371,89</t>
+          <t>83,17; 370,88</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0,07; 172,09</t>
+          <t>3,71; 191,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 54,38</t>
+          <t>-70,81; 51,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76,31; 381,76</t>
+          <t>72,29; 394,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>51,34; 318,32</t>
+          <t>51,27; 320,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-83,69; 18,19</t>
+          <t>-83,33; 17,62</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>107,26; 303,67</t>
+          <t>101,83; 290,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>49,16; 186,77</t>
+          <t>38,93; 186,75</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 0,61</t>
+          <t>-69,97; 1,1</t>
         </is>
       </c>
     </row>
